--- a/product_data_collection/refined_grocery_csv_for_classification/VLOOKUP 함수용 표.xlsx
+++ b/product_data_collection/refined_grocery_csv_for_classification/VLOOKUP 함수용 표.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LG\OneDrive\Desktop\REF_Classification_For_Ingredient_Recognition\ML_dataset_smapled\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LG\OneDrive\Desktop\REF_Classification_For_Ingredient_Recognition\product_data_collection\refined_grocery_csv_for_classification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBD70C9-898A-4A22-A964-5647486FA6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755532F0-ABB4-4273-BE89-ECC4892E8F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6960" yWindow="465" windowWidth="18570" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="1185" windowWidth="16770" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VLOOKUP 함수용 카테고리" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="카테고리매핑">'VLOOKUP 함수용 카테고리'!$C$1:$D$58</definedName>
     <definedName name="카테고리표">'VLOOKUP 함수용 카테고리'!$A$1:$B$54</definedName>
     <definedName name="카테고리표1">'VLOOKUP 함수용 카테고리'!$A$1:$B$55</definedName>
   </definedNames>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="140">
   <si>
     <t>ALCOHOL</t>
   </si>
@@ -292,6 +293,465 @@
   </si>
   <si>
     <t>SIMPLE_PROCESSED</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>어란</t>
+  </si>
+  <si>
+    <t>어란</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAW_SEAFOOD</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>술</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전통주</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>맥주</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>소주</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 주류</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>채소/곡물류</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>채소</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>버섯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>쌀/잡곡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>콩/두부</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>육류/계란</t>
+  </si>
+  <si>
+    <r>
+      <t>육류</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>계란</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>가공육</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>햄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>소시지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>수산물</t>
+  </si>
+  <si>
+    <r>
+      <t>조개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전복</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>새우</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>게</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>멸치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>건어물</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>오징어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>문어</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>미역</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>다시마</t>
+    </r>
+  </si>
+  <si>
+    <t>어육가공식품</t>
+  </si>
+  <si>
+    <r>
+      <t>과일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>견과류</t>
+    </r>
+  </si>
+  <si>
+    <t>과일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>견과류</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉동과일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>간편식</t>
+  </si>
+  <si>
+    <t>간편식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조미료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>식용유</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기름</t>
+    </r>
+  </si>
+  <si>
+    <t>양념/소스</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가루분말</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>향신료/허브</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>음료</t>
+  </si>
+  <si>
+    <t>음료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이온음료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주스</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>커피/차</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>생수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>유제품</t>
+  </si>
+  <si>
+    <t>유제품</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>우유/두유</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>요거트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>치즈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>버터/생크림</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>간식류</t>
+  </si>
+  <si>
+    <t>간식류</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>빵류</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>디저트/케이크</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>과자/스낵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>초콜릿/사탕</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>상온식품</t>
+  </si>
+  <si>
+    <t>상온식품</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>참치/스팸캔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김/자반</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>잼/스프레드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시리얼</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -299,7 +759,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -334,6 +794,21 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -355,11 +830,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -578,475 +1054,832 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
     <col min="2" max="2" width="30.42578125" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C1" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C6" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C7" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C10" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C13" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C15" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C16" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C17" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C18" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C19" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C20" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C21" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C22" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C23" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C24" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C25" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C26" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C27" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C28" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C29" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C30" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C32" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C33" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C34" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C35" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C36" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C37" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C38" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C39" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C40" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C41" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C42" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C43" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C44" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C45" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C46" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C47" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C48" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C49" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C50" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C51" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C52" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C53" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>74</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>76</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C56" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>78</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>81</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
